--- a/data/CL32.xlsx
+++ b/data/CL32.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adane\dm_tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6198E99E-CA81-4432-A651-54F50DD9FBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C227AC-D3E7-4EDC-A9F1-DE7DB4B97E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
@@ -929,7 +929,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -937,15 +937,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1285,3916 +1301,4261 @@
   <cols>
     <col min="1" max="1" width="46.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="96.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" customWidth="1"/>
+    <col min="6" max="6" width="29.85546875" customWidth="1"/>
+    <col min="7" max="7" width="38.28515625" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="31.28515625" customWidth="1"/>
+    <col min="10" max="10" width="34.28515625" customWidth="1"/>
     <col min="11" max="11" width="73.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>46302</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>46069</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>46279</v>
       </c>
-      <c r="G2">
-        <v>-17</v>
-      </c>
-      <c r="H2">
-        <v>-17</v>
-      </c>
-      <c r="I2">
+      <c r="G2" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H2" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I2" s="1">
         <v>92</v>
       </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>46302</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>46069</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>46279</v>
       </c>
-      <c r="G3">
-        <v>-17</v>
-      </c>
-      <c r="H3">
-        <v>-17</v>
-      </c>
-      <c r="I3">
+      <c r="G3" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H3" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I3" s="1">
         <v>82</v>
       </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>46302</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>46069</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>46279</v>
       </c>
-      <c r="G4">
-        <v>-17</v>
-      </c>
-      <c r="H4">
-        <v>-17</v>
-      </c>
-      <c r="I4">
+      <c r="G4" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H4" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I4" s="1">
         <v>9</v>
       </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="1">
+      <c r="D5" s="1"/>
+      <c r="E5" s="2">
         <v>46069</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="F5" s="1"/>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
         <v>1</v>
       </c>
+      <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="2">
         <v>46290</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>46302</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>46267</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>46279</v>
       </c>
-      <c r="G6">
-        <v>-17</v>
-      </c>
-      <c r="H6">
-        <v>-17</v>
-      </c>
-      <c r="I6">
+      <c r="G6" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H6" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I6" s="1">
         <v>9</v>
       </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2">
         <v>46279</v>
       </c>
-      <c r="G7">
-        <v>-17</v>
-      </c>
-      <c r="H7">
-        <v>-17</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
+      <c r="G7" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H7" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="1">
+      <c r="B8" s="1"/>
+      <c r="C8" s="2">
         <v>46185</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="2">
         <v>46289</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>46161</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>46266</v>
       </c>
-      <c r="G8">
-        <v>-17</v>
-      </c>
-      <c r="H8">
-        <v>-17</v>
-      </c>
-      <c r="I8">
+      <c r="G8" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H8" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I8" s="1">
         <v>73</v>
       </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="1">
+      <c r="C9" s="1"/>
+      <c r="D9" s="2">
         <v>46185</v>
       </c>
-      <c r="F9" s="1">
+      <c r="E9" s="1"/>
+      <c r="F9" s="2">
         <v>46161</v>
       </c>
-      <c r="G9">
-        <v>-17</v>
-      </c>
-      <c r="H9">
+      <c r="G9" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H9" s="1">
         <v>56</v>
       </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="1">
+      <c r="C10" s="1"/>
+      <c r="D10" s="2">
         <v>46202</v>
       </c>
-      <c r="F10" s="1">
+      <c r="E10" s="1"/>
+      <c r="F10" s="2">
         <v>46177</v>
       </c>
-      <c r="G10">
-        <v>-17</v>
-      </c>
-      <c r="H10">
+      <c r="G10" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H10" s="1">
         <v>46</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="1">
+      <c r="C11" s="1"/>
+      <c r="D11" s="2">
         <v>46289</v>
       </c>
-      <c r="F11" s="1">
+      <c r="E11" s="1"/>
+      <c r="F11" s="2">
         <v>46266</v>
       </c>
-      <c r="G11">
-        <v>-17</v>
-      </c>
-      <c r="H11">
-        <v>-17</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
+      <c r="G11" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H11" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="1">
+      <c r="C12" s="1"/>
+      <c r="D12" s="2">
         <v>46289</v>
       </c>
-      <c r="F12" s="1">
+      <c r="E12" s="1"/>
+      <c r="F12" s="2">
         <v>46266</v>
       </c>
-      <c r="G12">
-        <v>-17</v>
-      </c>
-      <c r="H12">
-        <v>-17</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
+      <c r="G12" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H12" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>46122</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <v>46135</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>-11</v>
       </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="1">
+      <c r="D14" s="1"/>
+      <c r="E14" s="2">
         <v>46122</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2">
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>1</v>
       </c>
+      <c r="K14" s="1"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="1">
+      <c r="C16" s="1"/>
+      <c r="D16" s="2">
         <v>46135</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2">
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="2">
         <v>46174</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>46069</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="2">
         <v>46143</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>-19</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>36</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="1">
+      <c r="D19" s="1"/>
+      <c r="E19" s="2">
         <v>46069</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2">
+      <c r="F19" s="1"/>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="1">
+      <c r="D20" s="1"/>
+      <c r="E20" s="2">
         <v>46069</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2">
+      <c r="F20" s="1"/>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="1">
+      <c r="D21" s="1"/>
+      <c r="E21" s="2">
         <v>46093</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
+      <c r="F21" s="1"/>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="1">
+      <c r="D22" s="1"/>
+      <c r="E22" s="2">
         <v>46094</v>
       </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
+      <c r="F22" s="1"/>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="1">
+      <c r="D23" s="1"/>
+      <c r="E23" s="2">
         <v>46094</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2">
+      <c r="F23" s="1"/>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="1">
+      <c r="D24" s="1"/>
+      <c r="E24" s="2">
         <v>46101</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2">
+      <c r="F24" s="1"/>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="1">
+      <c r="D25" s="1"/>
+      <c r="E25" s="2">
         <v>46101</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
+      <c r="F25" s="1"/>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="1">
+      <c r="D26" s="1"/>
+      <c r="E26" s="2">
         <v>46101</v>
       </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2">
+      <c r="F26" s="1"/>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E27" s="1">
+      <c r="D27" s="1"/>
+      <c r="E27" s="2">
         <v>46101</v>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2">
+      <c r="F27" s="1"/>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E28" s="1">
+      <c r="D28" s="1"/>
+      <c r="E28" s="2">
         <v>46101</v>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2">
+      <c r="F28" s="1"/>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E29" s="1">
+      <c r="D29" s="1"/>
+      <c r="E29" s="2">
         <v>46101</v>
       </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2">
+      <c r="F29" s="1"/>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E30" s="1">
+      <c r="D30" s="1"/>
+      <c r="E30" s="2">
         <v>46143</v>
       </c>
-      <c r="G30">
+      <c r="F30" s="1"/>
+      <c r="G30" s="1">
         <v>-19</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>36</v>
       </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C31" t="s">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="2">
         <v>46069</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="2">
         <v>46108</v>
       </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="2">
         <v>46069</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="2">
         <v>46073</v>
       </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2">
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>1</v>
       </c>
+      <c r="K32" s="1"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="2">
         <v>46076</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="2">
         <v>46080</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33" s="2">
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>1</v>
       </c>
+      <c r="K33" s="1"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="2">
         <v>46090</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="2">
         <v>46090</v>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2">
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3">
         <v>1</v>
       </c>
+      <c r="K34" s="1"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="2">
         <v>46090</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="2">
         <v>46094</v>
       </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35" s="2">
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>1</v>
       </c>
+      <c r="K35" s="1"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="2">
         <v>46097</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="2">
         <v>46108</v>
       </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2">
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3">
         <v>1</v>
       </c>
+      <c r="K36" s="1"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C37" t="s">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="2">
         <v>46289</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="2">
         <v>46097</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="2">
         <v>46266</v>
       </c>
-      <c r="G37">
-        <v>-17</v>
-      </c>
-      <c r="H37">
-        <v>-17</v>
-      </c>
-      <c r="I37">
+      <c r="G37" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H37" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I37" s="1">
         <v>83</v>
       </c>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C38" t="s">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39" s="2">
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3">
         <v>1</v>
       </c>
+      <c r="K39" s="1"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C40" t="s">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="2">
         <v>46185</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="2">
         <v>46111</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="2">
         <v>46164</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="1">
         <v>-14</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="1">
         <v>21</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="1">
         <v>10</v>
       </c>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="2">
         <v>46111</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="2">
         <v>46135</v>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41" s="2">
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>1</v>
       </c>
+      <c r="K41" s="1"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="2">
         <v>46111</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="2">
         <v>46135</v>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42" s="2">
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>1</v>
       </c>
+      <c r="K42" s="1"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="2">
         <v>46122</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="2">
         <v>46135</v>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43" s="2">
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
         <v>1</v>
       </c>
+      <c r="K43" s="1"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="2">
         <v>46136</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="2">
         <v>46142</v>
       </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44" s="2">
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
         <v>1</v>
       </c>
+      <c r="K44" s="1"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" s="2">
         <v>46178</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="2">
         <v>46143</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="2">
         <v>46164</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="1">
         <v>-9</v>
       </c>
-      <c r="H45">
-        <v>-17</v>
-      </c>
-      <c r="I45">
+      <c r="H45" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I45" s="1">
         <v>5</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="4">
         <v>0.66669999999999996</v>
       </c>
+      <c r="K45" s="1"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="2">
         <v>46178</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="2">
         <v>46143</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="2">
         <v>46164</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="1">
         <v>-9</v>
       </c>
-      <c r="H46">
-        <v>-17</v>
-      </c>
-      <c r="I46">
+      <c r="H46" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I46" s="1">
         <v>5</v>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="4">
         <v>0.66669999999999996</v>
       </c>
+      <c r="K46" s="1"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E47" s="1">
+      <c r="D47" s="1"/>
+      <c r="E47" s="2">
         <v>46143</v>
       </c>
-      <c r="G47">
+      <c r="F47" s="1"/>
+      <c r="G47" s="1">
         <v>-13</v>
       </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47" s="2">
+      <c r="H47" s="1"/>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
         <v>1</v>
       </c>
-      <c r="K47" t="s">
+      <c r="K47" s="1" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="2">
         <v>46174</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" s="2">
         <v>46185</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="2">
         <v>46143</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="2">
         <v>46157</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="1">
         <v>-19</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="1">
         <v>-7</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="1">
         <v>10</v>
       </c>
-      <c r="J48" s="2">
-        <v>0</v>
-      </c>
+      <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C49" t="s">
+      <c r="B49" s="1"/>
+      <c r="C49" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="2">
         <v>46206</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="2">
         <v>46111</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="2">
         <v>46183</v>
       </c>
-      <c r="G49">
-        <v>-17</v>
-      </c>
-      <c r="H49">
+      <c r="G49" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H49" s="1">
         <v>-12</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="1">
         <v>25</v>
       </c>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="2">
         <v>46111</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="2">
         <v>46114</v>
       </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50" s="2">
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3">
         <v>1</v>
       </c>
+      <c r="K50" s="1"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="2">
         <v>46111</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="2">
         <v>46114</v>
       </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51" s="2">
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3">
         <v>1</v>
       </c>
+      <c r="K51" s="1"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="2">
         <v>46111</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="2">
         <v>46114</v>
       </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2">
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>1</v>
       </c>
+      <c r="K52" s="1"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="2">
         <v>46111</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="2">
         <v>46114</v>
       </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53" s="2">
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3">
         <v>1</v>
       </c>
+      <c r="K53" s="1"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D54" t="s">
+      <c r="C54" s="1"/>
+      <c r="D54" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F54" s="1">
+      <c r="E54" s="1"/>
+      <c r="F54" s="2">
         <v>46147</v>
       </c>
-      <c r="G54">
-        <v>-17</v>
-      </c>
-      <c r="H54">
-        <v>-17</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2">
-        <v>0</v>
-      </c>
-      <c r="K54" t="s">
+      <c r="G54" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H54" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>0</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="2">
         <v>46174</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="2">
         <v>46178</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="2">
         <v>46148</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="2">
         <v>46154</v>
       </c>
-      <c r="G55">
-        <v>-17</v>
-      </c>
-      <c r="H55">
-        <v>-17</v>
-      </c>
-      <c r="I55">
+      <c r="G55" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H55" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I55" s="1">
         <v>5</v>
       </c>
-      <c r="J55" s="2">
-        <v>0</v>
-      </c>
+      <c r="J55" s="3">
+        <v>0</v>
+      </c>
+      <c r="K55" s="1"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="2">
         <v>46181</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" s="2">
         <v>46185</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="2">
         <v>46155</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="2">
         <v>46161</v>
       </c>
-      <c r="G56">
-        <v>-17</v>
-      </c>
-      <c r="H56">
-        <v>-17</v>
-      </c>
-      <c r="I56">
+      <c r="G56" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H56" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I56" s="1">
         <v>5</v>
       </c>
-      <c r="J56" s="2">
-        <v>0</v>
-      </c>
+      <c r="J56" s="3">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C57" s="2">
         <v>46188</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" s="2">
         <v>46199</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="2">
         <v>46162</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="2">
         <v>46176</v>
       </c>
-      <c r="G57">
-        <v>-17</v>
-      </c>
-      <c r="H57">
+      <c r="G57" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H57" s="1">
         <v>-12</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="1">
         <v>10</v>
       </c>
-      <c r="J57" s="2">
-        <v>0</v>
-      </c>
+      <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C58" s="2">
         <v>46202</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" s="2">
         <v>46206</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="2">
         <v>46177</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="2">
         <v>46183</v>
       </c>
-      <c r="G58">
-        <v>-17</v>
-      </c>
-      <c r="H58">
+      <c r="G58" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H58" s="1">
         <v>-12</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="1">
         <v>5</v>
       </c>
-      <c r="J58" s="2">
-        <v>0</v>
-      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="A59" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C59" t="s">
+      <c r="B59" s="1"/>
+      <c r="C59" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" s="2">
         <v>46213</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="2">
         <v>46104</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="2">
         <v>46190</v>
       </c>
-      <c r="G59">
-        <v>-17</v>
-      </c>
-      <c r="H59">
+      <c r="G59" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H59" s="1">
         <v>1</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="1">
         <v>30</v>
       </c>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="A60" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C60" t="s">
+      <c r="B60" s="1"/>
+      <c r="C60" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D60" s="2">
         <v>46199</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="2">
         <v>46111</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="2">
         <v>46176</v>
       </c>
-      <c r="G60">
-        <v>-17</v>
-      </c>
-      <c r="H60">
-        <v>-17</v>
-      </c>
-      <c r="I60">
+      <c r="G60" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H60" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I60" s="1">
         <v>20</v>
       </c>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="2">
         <v>46111</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="2">
         <v>46114</v>
       </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61" s="2">
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>1</v>
       </c>
+      <c r="K61" s="1"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62" s="2">
         <v>46119</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="2">
         <v>46125</v>
       </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62" s="2">
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>1</v>
       </c>
+      <c r="K62" s="1"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E63" s="2">
         <v>46126</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="2">
         <v>46132</v>
       </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63" s="2">
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3">
         <v>1</v>
       </c>
+      <c r="K63" s="1"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64" s="2">
         <v>46133</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="2">
         <v>46150</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="1">
         <v>-10</v>
       </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64" s="2">
+      <c r="H64" s="1"/>
+      <c r="I64" s="1">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="K64" s="1"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" s="2">
         <v>46174</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="2">
         <v>46153</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="2">
         <v>46157</v>
       </c>
-      <c r="G65">
+      <c r="G65" s="1">
         <v>-10</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="1">
         <v>2</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="1">
         <v>1</v>
       </c>
-      <c r="J65" s="2">
+      <c r="J65" s="3">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="K65" s="1"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="2">
         <v>46188</v>
       </c>
-      <c r="D66" s="1">
+      <c r="D66" s="2">
         <v>46199</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E66" s="2">
         <v>46162</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="2">
         <v>46176</v>
       </c>
-      <c r="G66">
-        <v>-17</v>
-      </c>
-      <c r="H66">
-        <v>-17</v>
-      </c>
-      <c r="I66">
+      <c r="G66" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H66" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I66" s="1">
         <v>10</v>
       </c>
-      <c r="J66" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="J66" s="3">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C67" t="s">
+      <c r="B67" s="1"/>
+      <c r="C67" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="2">
         <v>46111</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="2">
         <v>46153</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="1">
         <v>-9</v>
       </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="H67" s="1"/>
+      <c r="I67" s="1">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68" s="2">
         <v>46111</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="2">
         <v>46122</v>
       </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68" s="2">
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="K68" s="1"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E69" s="2">
         <v>46125</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="2">
         <v>46136</v>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69" s="2">
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="K69" s="1"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70" s="2">
         <v>46139</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="2">
         <v>46153</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="1">
         <v>-9</v>
       </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70" s="2">
+      <c r="H70" s="1"/>
+      <c r="I70" s="1">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="K70" s="1"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71" s="2">
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="K71" s="1"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D72" t="s">
+      <c r="C72" s="1"/>
+      <c r="D72" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72" s="2">
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="K72" s="1"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C73" t="s">
+      <c r="B73" s="1"/>
+      <c r="C73" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73" s="2">
         <v>46104</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="2">
         <v>46136</v>
       </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1">
+        <v>0</v>
+      </c>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E74" s="2">
         <v>46104</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="2">
         <v>46129</v>
       </c>
-      <c r="G74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74" s="2">
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="K74" s="1"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E75" s="2">
         <v>46111</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75" s="2">
         <v>46129</v>
       </c>
-      <c r="G75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75" s="2">
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="K75" s="1"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E76" s="2">
         <v>46132</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="2">
         <v>46136</v>
       </c>
-      <c r="G76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76" s="2">
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="K76" s="1"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C77" s="1">
+      <c r="B77" s="1"/>
+      <c r="C77" s="2">
         <v>46202</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D77" s="2">
         <v>46213</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E77" s="2">
         <v>46177</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="2">
         <v>46190</v>
       </c>
-      <c r="G77">
-        <v>-17</v>
-      </c>
-      <c r="H77">
-        <v>-17</v>
-      </c>
-      <c r="I77">
+      <c r="G77" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H77" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I77" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C78" s="1">
+      <c r="C78" s="2">
         <v>46202</v>
       </c>
-      <c r="E78" s="1">
+      <c r="D78" s="1"/>
+      <c r="E78" s="2">
         <v>46177</v>
       </c>
-      <c r="G78">
-        <v>-17</v>
-      </c>
-      <c r="H78">
-        <v>-17</v>
-      </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
-      <c r="J78" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="F78" s="1"/>
+      <c r="G78" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H78" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I78" s="1">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3">
+        <v>0</v>
+      </c>
+      <c r="K78" s="1"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C79" s="1">
+      <c r="C79" s="2">
         <v>46202</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D79" s="2">
         <v>46213</v>
       </c>
-      <c r="E79" s="1">
+      <c r="E79" s="2">
         <v>46177</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79" s="2">
         <v>46190</v>
       </c>
-      <c r="G79">
-        <v>-17</v>
-      </c>
-      <c r="H79">
-        <v>-17</v>
-      </c>
-      <c r="I79">
+      <c r="G79" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H79" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I79" s="1">
         <v>10</v>
       </c>
-      <c r="J79" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="J79" s="3">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C80" t="s">
+      <c r="B80" s="1"/>
+      <c r="C80" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D80" s="2">
         <v>46289</v>
       </c>
-      <c r="E80" s="1">
+      <c r="E80" s="2">
         <v>46097</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80" s="2">
         <v>46266</v>
       </c>
-      <c r="G80">
-        <v>-17</v>
-      </c>
-      <c r="H80">
-        <v>-17</v>
-      </c>
-      <c r="I80">
+      <c r="G80" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H80" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I80" s="1">
         <v>83</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C81" t="s">
+      <c r="B81" s="1"/>
+      <c r="C81" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D81" s="2">
         <v>46206</v>
       </c>
-      <c r="E81" s="1">
+      <c r="E81" s="2">
         <v>46097</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="2">
         <v>46183</v>
       </c>
-      <c r="G81">
-        <v>-17</v>
-      </c>
-      <c r="H81">
+      <c r="G81" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H81" s="1">
         <v>21</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E82" s="1">
+      <c r="E82" s="2">
         <v>46097</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="2">
         <v>46101</v>
       </c>
-      <c r="G82">
-        <v>0</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82" s="2">
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="K82" s="1"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C83" s="1">
+      <c r="C83" s="2">
         <v>46188</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D83" s="2">
         <v>46192</v>
       </c>
-      <c r="E83" s="1">
+      <c r="E83" s="2">
         <v>46162</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="2">
         <v>46169</v>
       </c>
-      <c r="G83">
-        <v>-17</v>
-      </c>
-      <c r="H83">
+      <c r="G83" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H83" s="1">
         <v>21</v>
       </c>
-      <c r="I83">
+      <c r="I83" s="1">
         <v>5</v>
       </c>
-      <c r="J83" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="1"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C84" s="1">
+      <c r="C84" s="2">
         <v>46195</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D84" s="2">
         <v>46206</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E84" s="2">
         <v>46170</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84" s="2">
         <v>46183</v>
       </c>
-      <c r="G84">
-        <v>-17</v>
-      </c>
-      <c r="H84">
+      <c r="G84" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H84" s="1">
         <v>21</v>
       </c>
-      <c r="I84">
+      <c r="I84" s="1">
         <v>10</v>
       </c>
-      <c r="J84" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="J84" s="3">
+        <v>0</v>
+      </c>
+      <c r="K84" s="1"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C85" s="1">
+      <c r="B85" s="1"/>
+      <c r="C85" s="2">
         <v>46216</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D85" s="2">
         <v>46260</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E85" s="2">
         <v>46191</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85" s="2">
         <v>46237</v>
       </c>
-      <c r="G85">
-        <v>-17</v>
-      </c>
-      <c r="H85">
-        <v>-17</v>
-      </c>
-      <c r="I85">
+      <c r="G85" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H85" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I85" s="1">
         <v>33</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C86" s="1">
+      <c r="B86" s="1"/>
+      <c r="C86" s="2">
         <v>46216</v>
       </c>
-      <c r="D86" s="1">
+      <c r="D86" s="2">
         <v>46255</v>
       </c>
-      <c r="E86" s="1">
+      <c r="E86" s="2">
         <v>46191</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86" s="2">
         <v>46232</v>
       </c>
-      <c r="G86">
-        <v>-17</v>
-      </c>
-      <c r="H86">
-        <v>-17</v>
-      </c>
-      <c r="I86">
+      <c r="G86" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H86" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I86" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C87" s="1">
+      <c r="C87" s="2">
         <v>46216</v>
       </c>
-      <c r="D87" s="1">
+      <c r="D87" s="2">
         <v>46227</v>
       </c>
-      <c r="E87" s="1">
+      <c r="E87" s="2">
         <v>46191</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87" s="2">
         <v>46204</v>
       </c>
-      <c r="G87">
-        <v>-17</v>
-      </c>
-      <c r="H87">
-        <v>-17</v>
-      </c>
-      <c r="I87">
+      <c r="G87" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H87" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I87" s="1">
         <v>10</v>
       </c>
-      <c r="J87" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="J87" s="3">
+        <v>0</v>
+      </c>
+      <c r="K87" s="1"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C88" s="1">
+      <c r="C88" s="2">
         <v>46230</v>
       </c>
-      <c r="D88" s="1">
+      <c r="D88" s="2">
         <v>46234</v>
       </c>
-      <c r="E88" s="1">
+      <c r="E88" s="2">
         <v>46205</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88" s="2">
         <v>46211</v>
       </c>
-      <c r="G88">
-        <v>-17</v>
-      </c>
-      <c r="H88">
-        <v>-17</v>
-      </c>
-      <c r="I88">
+      <c r="G88" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H88" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I88" s="1">
         <v>5</v>
       </c>
-      <c r="J88" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="J88" s="3">
+        <v>0</v>
+      </c>
+      <c r="K88" s="1"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C89" s="1">
+      <c r="C89" s="2">
         <v>46237</v>
       </c>
-      <c r="D89" s="1">
+      <c r="D89" s="2">
         <v>46248</v>
       </c>
-      <c r="E89" s="1">
+      <c r="E89" s="2">
         <v>46212</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89" s="2">
         <v>46225</v>
       </c>
-      <c r="G89">
-        <v>-17</v>
-      </c>
-      <c r="H89">
-        <v>-17</v>
-      </c>
-      <c r="I89">
+      <c r="G89" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H89" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I89" s="1">
         <v>10</v>
       </c>
-      <c r="J89" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="1"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C90" s="1">
+      <c r="C90" s="2">
         <v>46251</v>
       </c>
-      <c r="D90" s="1">
+      <c r="D90" s="2">
         <v>46255</v>
       </c>
-      <c r="E90" s="1">
+      <c r="E90" s="2">
         <v>46226</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90" s="2">
         <v>46232</v>
       </c>
-      <c r="G90">
-        <v>-17</v>
-      </c>
-      <c r="H90">
-        <v>-17</v>
-      </c>
-      <c r="I90">
+      <c r="G90" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H90" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I90" s="1">
         <v>5</v>
       </c>
-      <c r="J90" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="J90" s="3">
+        <v>0</v>
+      </c>
+      <c r="K90" s="1"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C91" s="1">
+      <c r="B91" s="1"/>
+      <c r="C91" s="2">
         <v>46216</v>
       </c>
-      <c r="D91" s="1">
+      <c r="D91" s="2">
         <v>46238</v>
       </c>
-      <c r="E91" s="1">
+      <c r="E91" s="2">
         <v>46191</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91" s="2">
         <v>46213</v>
       </c>
-      <c r="G91">
-        <v>-17</v>
-      </c>
-      <c r="H91">
+      <c r="G91" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H91" s="1">
         <v>-16</v>
       </c>
-      <c r="I91">
+      <c r="I91" s="1">
         <v>17</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C92" s="1">
+      <c r="C92" s="2">
         <v>46216</v>
       </c>
-      <c r="D92" s="1">
+      <c r="D92" s="2">
         <v>46224</v>
       </c>
-      <c r="E92" s="1">
+      <c r="E92" s="2">
         <v>46191</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92" s="2">
         <v>46199</v>
       </c>
-      <c r="G92">
-        <v>-17</v>
-      </c>
-      <c r="H92">
+      <c r="G92" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H92" s="1">
         <v>-16</v>
       </c>
-      <c r="I92">
+      <c r="I92" s="1">
         <v>7</v>
       </c>
-      <c r="J92" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="J92" s="3">
+        <v>0</v>
+      </c>
+      <c r="K92" s="1"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C93" s="1">
+      <c r="C93" s="2">
         <v>46225</v>
       </c>
-      <c r="D93" s="1">
+      <c r="D93" s="2">
         <v>46231</v>
       </c>
-      <c r="E93" s="1">
+      <c r="E93" s="2">
         <v>46202</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93" s="2">
         <v>46206</v>
       </c>
-      <c r="G93">
-        <v>-17</v>
-      </c>
-      <c r="H93">
+      <c r="G93" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H93" s="1">
         <v>-16</v>
       </c>
-      <c r="I93">
+      <c r="I93" s="1">
         <v>5</v>
       </c>
-      <c r="J93" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="J93" s="3">
+        <v>0</v>
+      </c>
+      <c r="K93" s="1"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C94" s="1">
+      <c r="C94" s="2">
         <v>46232</v>
       </c>
-      <c r="D94" s="1">
+      <c r="D94" s="2">
         <v>46238</v>
       </c>
-      <c r="E94" s="1">
+      <c r="E94" s="2">
         <v>46209</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94" s="2">
         <v>46213</v>
       </c>
-      <c r="G94">
-        <v>-17</v>
-      </c>
-      <c r="H94">
+      <c r="G94" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H94" s="1">
         <v>-16</v>
       </c>
-      <c r="I94">
+      <c r="I94" s="1">
         <v>5</v>
       </c>
-      <c r="J94" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="1"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C95" s="1">
+      <c r="B95" s="1"/>
+      <c r="C95" s="2">
         <v>46239</v>
       </c>
-      <c r="D95" s="1">
+      <c r="D95" s="2">
         <v>46259</v>
       </c>
-      <c r="E95" s="1">
+      <c r="E95" s="2">
         <v>46216</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95" s="2">
         <v>46234</v>
       </c>
-      <c r="G95">
-        <v>-17</v>
-      </c>
-      <c r="H95">
+      <c r="G95" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H95" s="1">
         <v>-16</v>
       </c>
-      <c r="I95">
+      <c r="I95" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C96" s="1">
+      <c r="C96" s="2">
         <v>46239</v>
       </c>
-      <c r="D96" s="1">
+      <c r="D96" s="2">
         <v>46245</v>
       </c>
-      <c r="E96" s="1">
+      <c r="E96" s="2">
         <v>46216</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96" s="2">
         <v>46220</v>
       </c>
-      <c r="G96">
-        <v>-17</v>
-      </c>
-      <c r="H96">
+      <c r="G96" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H96" s="1">
         <v>-16</v>
       </c>
-      <c r="I96">
+      <c r="I96" s="1">
         <v>5</v>
       </c>
-      <c r="J96" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="1"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C97" s="1">
+      <c r="C97" s="2">
         <v>46246</v>
       </c>
-      <c r="D97" s="1">
+      <c r="D97" s="2">
         <v>46252</v>
       </c>
-      <c r="E97" s="1">
+      <c r="E97" s="2">
         <v>46223</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97" s="2">
         <v>46227</v>
       </c>
-      <c r="G97">
-        <v>-17</v>
-      </c>
-      <c r="H97">
+      <c r="G97" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H97" s="1">
         <v>-16</v>
       </c>
-      <c r="I97">
+      <c r="I97" s="1">
         <v>5</v>
       </c>
-      <c r="J97" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="J97" s="3">
+        <v>0</v>
+      </c>
+      <c r="K97" s="1"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C98" s="1">
+      <c r="C98" s="2">
         <v>46253</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D98" s="2">
         <v>46259</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E98" s="2">
         <v>46230</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="2">
         <v>46234</v>
       </c>
-      <c r="G98">
-        <v>-17</v>
-      </c>
-      <c r="H98">
+      <c r="G98" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H98" s="1">
         <v>-16</v>
       </c>
-      <c r="I98">
+      <c r="I98" s="1">
         <v>5</v>
       </c>
-      <c r="J98" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="J98" s="3">
+        <v>0</v>
+      </c>
+      <c r="K98" s="1"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C99" s="1">
+      <c r="B99" s="1"/>
+      <c r="C99" s="2">
         <v>46216</v>
       </c>
-      <c r="D99" s="1">
+      <c r="D99" s="2">
         <v>46220</v>
       </c>
-      <c r="E99" s="1">
+      <c r="E99" s="2">
         <v>46191</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99" s="2">
         <v>46197</v>
       </c>
-      <c r="G99">
-        <v>-17</v>
-      </c>
-      <c r="H99">
+      <c r="G99" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H99" s="1">
         <v>11</v>
       </c>
-      <c r="I99">
+      <c r="I99" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="J99" s="1"/>
+      <c r="K99" s="1"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C100" s="1">
+      <c r="C100" s="2">
         <v>46216</v>
       </c>
-      <c r="D100" s="1">
+      <c r="D100" s="2">
         <v>46220</v>
       </c>
-      <c r="E100" s="1">
+      <c r="E100" s="2">
         <v>46191</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100" s="2">
         <v>46197</v>
       </c>
-      <c r="G100">
-        <v>-17</v>
-      </c>
-      <c r="H100">
+      <c r="G100" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H100" s="1">
         <v>11</v>
       </c>
-      <c r="I100">
+      <c r="I100" s="1">
         <v>5</v>
       </c>
-      <c r="J100" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="1"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C101" s="1">
+      <c r="B101" s="1"/>
+      <c r="C101" s="2">
         <v>46258</v>
       </c>
-      <c r="D101" s="1">
+      <c r="D101" s="2">
         <v>46260</v>
       </c>
-      <c r="E101" s="1">
+      <c r="E101" s="2">
         <v>46233</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101" s="2">
         <v>46237</v>
       </c>
-      <c r="G101">
-        <v>-17</v>
-      </c>
-      <c r="H101">
-        <v>-17</v>
-      </c>
-      <c r="I101">
+      <c r="G101" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H101" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I101" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C102" s="1">
+      <c r="C102" s="2">
         <v>46258</v>
       </c>
-      <c r="D102" s="1">
+      <c r="D102" s="2">
         <v>46260</v>
       </c>
-      <c r="E102" s="1">
+      <c r="E102" s="2">
         <v>46233</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102" s="2">
         <v>46237</v>
       </c>
-      <c r="G102">
-        <v>-17</v>
-      </c>
-      <c r="H102">
-        <v>-17</v>
-      </c>
-      <c r="I102">
+      <c r="G102" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H102" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I102" s="1">
         <v>3</v>
       </c>
-      <c r="J102" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="1"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C103" s="1">
+      <c r="B103" s="1"/>
+      <c r="C103" s="2">
         <v>46237</v>
       </c>
-      <c r="D103" s="1">
+      <c r="D103" s="2">
         <v>46241</v>
       </c>
-      <c r="E103" s="1">
+      <c r="E103" s="2">
         <v>46212</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F103" s="2">
         <v>46218</v>
       </c>
-      <c r="G103">
-        <v>-17</v>
-      </c>
-      <c r="H103">
+      <c r="G103" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H103" s="1">
         <v>-4</v>
       </c>
-      <c r="I103">
+      <c r="I103" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="J103" s="1"/>
+      <c r="K103" s="1"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C104" s="1">
+      <c r="C104" s="2">
         <v>46237</v>
       </c>
-      <c r="D104" s="1">
+      <c r="D104" s="2">
         <v>46241</v>
       </c>
-      <c r="E104" s="1">
+      <c r="E104" s="2">
         <v>46212</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F104" s="2">
         <v>46218</v>
       </c>
-      <c r="G104">
-        <v>-17</v>
-      </c>
-      <c r="H104">
+      <c r="G104" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H104" s="1">
         <v>-4</v>
       </c>
-      <c r="I104">
+      <c r="I104" s="1">
         <v>5</v>
       </c>
-      <c r="J104" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="J104" s="3">
+        <v>0</v>
+      </c>
+      <c r="K104" s="1"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C105" s="1">
+      <c r="B105" s="1"/>
+      <c r="C105" s="2">
         <v>46174</v>
       </c>
-      <c r="D105" s="1">
+      <c r="D105" s="2">
         <v>46183</v>
       </c>
-      <c r="E105" s="1">
+      <c r="E105" s="2">
         <v>46154</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F105" s="2">
         <v>46169</v>
       </c>
-      <c r="G105">
+      <c r="G105" s="1">
         <v>-10</v>
       </c>
-      <c r="H105">
+      <c r="H105" s="1">
         <v>38</v>
       </c>
-      <c r="I105">
+      <c r="I105" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C106" s="1">
+      <c r="C106" s="2">
         <v>46174</v>
       </c>
-      <c r="D106" s="1">
+      <c r="D106" s="2">
         <v>46174</v>
       </c>
-      <c r="E106" s="1">
+      <c r="E106" s="2">
         <v>46154</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106" s="2">
         <v>46154</v>
       </c>
-      <c r="G106">
+      <c r="G106" s="1">
         <v>-12</v>
       </c>
-      <c r="H106">
+      <c r="H106" s="1">
         <v>38</v>
       </c>
-      <c r="I106">
-        <v>0</v>
-      </c>
-      <c r="J106" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="I106" s="1">
+        <v>0</v>
+      </c>
+      <c r="J106" s="3">
+        <v>0</v>
+      </c>
+      <c r="K106" s="1"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C107" s="1">
+      <c r="C107" s="2">
         <v>46174</v>
       </c>
-      <c r="D107" s="1">
+      <c r="D107" s="2">
         <v>46183</v>
       </c>
-      <c r="E107" s="1">
+      <c r="E107" s="2">
         <v>46155</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107" s="2">
         <v>46169</v>
       </c>
-      <c r="G107">
+      <c r="G107" s="1">
         <v>-10</v>
       </c>
-      <c r="H107">
+      <c r="H107" s="1">
         <v>38</v>
       </c>
-      <c r="I107">
+      <c r="I107" s="1">
         <v>8</v>
       </c>
-      <c r="J107" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="J107" s="3">
+        <v>0</v>
+      </c>
+      <c r="K107" s="1"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C108" s="1">
+      <c r="B108" s="1"/>
+      <c r="C108" s="2">
         <v>46216</v>
       </c>
-      <c r="D108" s="1">
+      <c r="D108" s="2">
         <v>46245</v>
       </c>
-      <c r="E108" s="1">
+      <c r="E108" s="2">
         <v>46191</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108" s="2">
         <v>46220</v>
       </c>
-      <c r="G108">
-        <v>-17</v>
-      </c>
-      <c r="H108">
+      <c r="G108" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H108" s="1">
         <v>-6</v>
       </c>
-      <c r="I108">
+      <c r="I108" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C109" s="1">
+      <c r="B109" s="1"/>
+      <c r="C109" s="2">
         <v>46216</v>
       </c>
-      <c r="D109" s="1">
+      <c r="D109" s="2">
         <v>46241</v>
       </c>
-      <c r="E109" s="1">
+      <c r="E109" s="2">
         <v>46191</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109" s="2">
         <v>46218</v>
       </c>
-      <c r="G109">
-        <v>-17</v>
-      </c>
-      <c r="H109">
+      <c r="G109" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H109" s="1">
         <v>-4</v>
       </c>
-      <c r="I109">
+      <c r="I109" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C110" s="1">
+      <c r="C110" s="2">
         <v>46216</v>
       </c>
-      <c r="D110" s="1">
+      <c r="D110" s="2">
         <v>46227</v>
       </c>
-      <c r="E110" s="1">
+      <c r="E110" s="2">
         <v>46191</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110" s="2">
         <v>46204</v>
       </c>
-      <c r="G110">
-        <v>-17</v>
-      </c>
-      <c r="H110">
+      <c r="G110" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H110" s="1">
         <v>6</v>
       </c>
-      <c r="I110">
+      <c r="I110" s="1">
         <v>10</v>
       </c>
-      <c r="J110" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="J110" s="3">
+        <v>0</v>
+      </c>
+      <c r="K110" s="1"/>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C111" s="1">
+      <c r="C111" s="2">
         <v>46237</v>
       </c>
-      <c r="D111" s="1">
+      <c r="D111" s="2">
         <v>46241</v>
       </c>
-      <c r="E111" s="1">
+      <c r="E111" s="2">
         <v>46212</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111" s="2">
         <v>46218</v>
       </c>
-      <c r="G111">
-        <v>-17</v>
-      </c>
-      <c r="H111">
+      <c r="G111" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H111" s="1">
         <v>-4</v>
       </c>
-      <c r="I111">
+      <c r="I111" s="1">
         <v>5</v>
       </c>
-      <c r="J111" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="J111" s="3">
+        <v>0</v>
+      </c>
+      <c r="K111" s="1"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C112" s="1">
+      <c r="C112" s="2">
         <v>46237</v>
       </c>
-      <c r="D112" s="1">
+      <c r="D112" s="2">
         <v>46241</v>
       </c>
-      <c r="E112" s="1">
+      <c r="E112" s="2">
         <v>46212</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112" s="2">
         <v>46218</v>
       </c>
-      <c r="G112">
-        <v>-17</v>
-      </c>
-      <c r="H112">
+      <c r="G112" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H112" s="1">
         <v>-4</v>
       </c>
-      <c r="I112">
+      <c r="I112" s="1">
         <v>5</v>
       </c>
-      <c r="J112" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="J112" s="3">
+        <v>0</v>
+      </c>
+      <c r="K112" s="1"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C113" s="1">
+      <c r="B113" s="1"/>
+      <c r="C113" s="2">
         <v>46216</v>
       </c>
-      <c r="D113" s="1">
+      <c r="D113" s="2">
         <v>46245</v>
       </c>
-      <c r="E113" s="1">
+      <c r="E113" s="2">
         <v>46191</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113" s="2">
         <v>46220</v>
       </c>
-      <c r="G113">
-        <v>-17</v>
-      </c>
-      <c r="H113">
+      <c r="G113" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H113" s="1">
         <v>-11</v>
       </c>
-      <c r="I113">
+      <c r="I113" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="J113" s="1"/>
+      <c r="K113" s="1"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C114" s="1">
+      <c r="C114" s="2">
         <v>46216</v>
       </c>
-      <c r="D114" s="1">
+      <c r="D114" s="2">
         <v>46218</v>
       </c>
-      <c r="E114" s="1">
+      <c r="E114" s="2">
         <v>46191</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114" s="2">
         <v>46195</v>
       </c>
-      <c r="G114">
-        <v>-17</v>
-      </c>
-      <c r="H114">
+      <c r="G114" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H114" s="1">
         <v>-11</v>
       </c>
-      <c r="I114">
+      <c r="I114" s="1">
         <v>3</v>
       </c>
-      <c r="J114" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="J114" s="3">
+        <v>0</v>
+      </c>
+      <c r="K114" s="1"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C115" s="1">
+      <c r="C115" s="2">
         <v>46219</v>
       </c>
-      <c r="D115" s="1">
+      <c r="D115" s="2">
         <v>46223</v>
       </c>
-      <c r="E115" s="1">
+      <c r="E115" s="2">
         <v>46196</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115" s="2">
         <v>46198</v>
       </c>
-      <c r="G115">
-        <v>-17</v>
-      </c>
-      <c r="H115">
+      <c r="G115" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H115" s="1">
         <v>-11</v>
       </c>
-      <c r="I115">
+      <c r="I115" s="1">
         <v>3</v>
       </c>
-      <c r="J115" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="J115" s="3">
+        <v>0</v>
+      </c>
+      <c r="K115" s="1"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C116" s="1">
+      <c r="C116" s="2">
         <v>46224</v>
       </c>
-      <c r="D116" s="1">
+      <c r="D116" s="2">
         <v>46226</v>
       </c>
-      <c r="E116" s="1">
+      <c r="E116" s="2">
         <v>46199</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116" s="2">
         <v>46203</v>
       </c>
-      <c r="G116">
-        <v>-17</v>
-      </c>
-      <c r="H116">
+      <c r="G116" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H116" s="1">
         <v>-11</v>
       </c>
-      <c r="I116">
+      <c r="I116" s="1">
         <v>3</v>
       </c>
-      <c r="J116" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="J116" s="3">
+        <v>0</v>
+      </c>
+      <c r="K116" s="1"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C117" s="1">
+      <c r="C117" s="2">
         <v>46227</v>
       </c>
-      <c r="D117" s="1">
+      <c r="D117" s="2">
         <v>46231</v>
       </c>
-      <c r="E117" s="1">
+      <c r="E117" s="2">
         <v>46204</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117" s="2">
         <v>46206</v>
       </c>
-      <c r="G117">
-        <v>-17</v>
-      </c>
-      <c r="H117">
+      <c r="G117" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H117" s="1">
         <v>-11</v>
       </c>
-      <c r="I117">
+      <c r="I117" s="1">
         <v>3</v>
       </c>
-      <c r="J117" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="J117" s="3">
+        <v>0</v>
+      </c>
+      <c r="K117" s="1"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C118" s="1">
+      <c r="C118" s="2">
         <v>46232</v>
       </c>
-      <c r="D118" s="1">
+      <c r="D118" s="2">
         <v>46245</v>
       </c>
-      <c r="E118" s="1">
+      <c r="E118" s="2">
         <v>46209</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118" s="2">
         <v>46220</v>
       </c>
-      <c r="G118">
-        <v>-17</v>
-      </c>
-      <c r="H118">
+      <c r="G118" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H118" s="1">
         <v>-11</v>
       </c>
-      <c r="I118">
+      <c r="I118" s="1">
         <v>10</v>
       </c>
-      <c r="J118" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="J118" s="3">
+        <v>0</v>
+      </c>
+      <c r="K118" s="1"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C119" s="1">
+      <c r="C119" s="2">
         <v>46232</v>
       </c>
-      <c r="D119" s="1">
+      <c r="D119" s="2">
         <v>46234</v>
       </c>
-      <c r="E119" s="1">
+      <c r="E119" s="2">
         <v>46209</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119" s="2">
         <v>46211</v>
       </c>
-      <c r="G119">
-        <v>-17</v>
-      </c>
-      <c r="H119">
+      <c r="G119" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H119" s="1">
         <v>-4</v>
       </c>
-      <c r="I119">
+      <c r="I119" s="1">
         <v>3</v>
       </c>
-      <c r="J119" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="J119" s="3">
+        <v>0</v>
+      </c>
+      <c r="K119" s="1"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C120" t="s">
+      <c r="B120" s="1"/>
+      <c r="C120" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D120" s="1">
+      <c r="D120" s="2">
         <v>46205</v>
       </c>
-      <c r="E120" s="1">
+      <c r="E120" s="2">
         <v>46139</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120" s="2">
         <v>46192</v>
       </c>
-      <c r="G120">
+      <c r="G120" s="1">
         <v>-9</v>
       </c>
-      <c r="H120">
+      <c r="H120" s="1">
         <v>22</v>
       </c>
-      <c r="I120">
+      <c r="I120" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="J120" s="1"/>
+      <c r="K120" s="1"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C121" t="s">
+      <c r="B121" s="1"/>
+      <c r="C121" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D121" s="1">
+      <c r="D121" s="2">
         <v>46205</v>
       </c>
-      <c r="E121" s="1">
+      <c r="E121" s="2">
         <v>46139</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121" s="2">
         <v>46192</v>
       </c>
-      <c r="G121">
+      <c r="G121" s="1">
         <v>-9</v>
       </c>
-      <c r="H121">
+      <c r="H121" s="1">
         <v>22</v>
       </c>
-      <c r="I121">
+      <c r="I121" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="J121" s="1"/>
+      <c r="K121" s="1"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122" s="2">
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1">
+        <v>0</v>
+      </c>
+      <c r="J122" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="K122" s="1"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D123" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E123" s="1">
+      <c r="E123" s="2">
         <v>46139</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F123" s="2">
         <v>46153</v>
       </c>
-      <c r="G123">
+      <c r="G123" s="1">
         <v>-10</v>
       </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123" s="2">
+      <c r="H123" s="1"/>
+      <c r="I123" s="1">
+        <v>0</v>
+      </c>
+      <c r="J123" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="K123" s="1"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E124" s="1">
+      <c r="E124" s="2">
         <v>46154</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124" s="2">
         <v>46156</v>
       </c>
-      <c r="G124">
+      <c r="G124" s="1">
         <v>-9</v>
       </c>
-      <c r="I124">
-        <v>0</v>
-      </c>
-      <c r="J124" s="2">
+      <c r="H124" s="1"/>
+      <c r="I124" s="1">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="K124" s="1"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D125" s="1">
+      <c r="D125" s="2">
         <v>46175</v>
       </c>
-      <c r="E125" s="1">
+      <c r="E125" s="2">
         <v>46154</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F125" s="2">
         <v>46160</v>
       </c>
-      <c r="G125">
+      <c r="G125" s="1">
         <v>-10</v>
       </c>
-      <c r="H125">
+      <c r="H125" s="1">
         <v>31</v>
       </c>
-      <c r="I125">
+      <c r="I125" s="1">
         <v>2</v>
       </c>
-      <c r="J125" s="2">
+      <c r="J125" s="3">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="K125" s="1"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="D126" s="1">
+      <c r="D126" s="2">
         <v>46184</v>
       </c>
-      <c r="E126" s="1">
+      <c r="E126" s="2">
         <v>46157</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F126" s="2">
         <v>46171</v>
       </c>
-      <c r="G126">
+      <c r="G126" s="1">
         <v>-9</v>
       </c>
-      <c r="H126">
+      <c r="H126" s="1">
         <v>22</v>
       </c>
-      <c r="I126">
+      <c r="I126" s="1">
         <v>9</v>
       </c>
-      <c r="J126" s="2">
+      <c r="J126" s="3">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="K126" s="1"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C127" s="1">
+      <c r="C127" s="2">
         <v>46176</v>
       </c>
-      <c r="D127" s="1">
+      <c r="D127" s="2">
         <v>46178</v>
       </c>
-      <c r="E127" s="1">
+      <c r="E127" s="2">
         <v>46161</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F127" s="2">
         <v>46163</v>
       </c>
-      <c r="G127">
+      <c r="G127" s="1">
         <v>-10</v>
       </c>
-      <c r="H127">
+      <c r="H127" s="1">
         <v>31</v>
       </c>
-      <c r="I127">
+      <c r="I127" s="1">
         <v>3</v>
       </c>
-      <c r="J127" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="J127" s="3">
+        <v>0</v>
+      </c>
+      <c r="K127" s="1"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C128" s="1">
+      <c r="C128" s="2">
         <v>46185</v>
       </c>
-      <c r="D128" s="1">
+      <c r="D128" s="2">
         <v>46198</v>
       </c>
-      <c r="E128" s="1">
+      <c r="E128" s="2">
         <v>46174</v>
       </c>
-      <c r="F128" s="1">
+      <c r="F128" s="2">
         <v>46185</v>
       </c>
-      <c r="G128">
+      <c r="G128" s="1">
         <v>-9</v>
       </c>
-      <c r="H128">
+      <c r="H128" s="1">
         <v>22</v>
       </c>
-      <c r="I128">
+      <c r="I128" s="1">
         <v>10</v>
       </c>
-      <c r="J128" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="J128" s="3">
+        <v>0</v>
+      </c>
+      <c r="K128" s="1"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C129" s="1">
+      <c r="C129" s="2">
         <v>46199</v>
       </c>
-      <c r="D129" s="1">
+      <c r="D129" s="2">
         <v>46205</v>
       </c>
-      <c r="E129" s="1">
+      <c r="E129" s="2">
         <v>46188</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F129" s="2">
         <v>46192</v>
       </c>
-      <c r="G129">
+      <c r="G129" s="1">
         <v>-9</v>
       </c>
-      <c r="H129">
+      <c r="H129" s="1">
         <v>22</v>
       </c>
-      <c r="I129">
+      <c r="I129" s="1">
         <v>5</v>
       </c>
-      <c r="J129" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="J129" s="3">
+        <v>0</v>
+      </c>
+      <c r="K129" s="1"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C130" t="s">
+      <c r="B130" s="1"/>
+      <c r="C130" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="D130" s="1">
+      <c r="D130" s="2">
         <v>46192</v>
       </c>
-      <c r="E130" s="1">
+      <c r="E130" s="2">
         <v>46157</v>
       </c>
-      <c r="F130" s="1">
+      <c r="F130" s="2">
         <v>46178</v>
       </c>
-      <c r="G130">
+      <c r="G130" s="1">
         <v>-10</v>
       </c>
-      <c r="H130">
+      <c r="H130" s="1">
         <v>31</v>
       </c>
-      <c r="I130">
+      <c r="I130" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="J130" s="1"/>
+      <c r="K130" s="1"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="D131" s="1">
+      <c r="D131" s="2">
         <v>46177</v>
       </c>
-      <c r="E131" s="1">
+      <c r="E131" s="2">
         <v>46157</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F131" s="2">
         <v>46163</v>
       </c>
-      <c r="G131">
+      <c r="G131" s="1">
         <v>-9</v>
       </c>
-      <c r="H131">
+      <c r="H131" s="1">
         <v>32</v>
       </c>
-      <c r="I131">
+      <c r="I131" s="1">
         <v>4</v>
       </c>
-      <c r="J131" s="2">
+      <c r="J131" s="3">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="K131" s="1"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C132" s="1">
+      <c r="C132" s="2">
         <v>46181</v>
       </c>
-      <c r="D132" s="1">
+      <c r="D132" s="2">
         <v>46185</v>
       </c>
-      <c r="E132" s="1">
+      <c r="E132" s="2">
         <v>46164</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F132" s="2">
         <v>46171</v>
       </c>
-      <c r="G132">
+      <c r="G132" s="1">
         <v>-10</v>
       </c>
-      <c r="H132">
+      <c r="H132" s="1">
         <v>31</v>
       </c>
-      <c r="I132">
+      <c r="I132" s="1">
         <v>5</v>
       </c>
-      <c r="J132" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="J132" s="3">
+        <v>0</v>
+      </c>
+      <c r="K132" s="1"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C133" s="1">
+      <c r="C133" s="2">
         <v>46188</v>
       </c>
-      <c r="D133" s="1">
+      <c r="D133" s="2">
         <v>46192</v>
       </c>
-      <c r="E133" s="1">
+      <c r="E133" s="2">
         <v>46174</v>
       </c>
-      <c r="F133" s="1">
+      <c r="F133" s="2">
         <v>46178</v>
       </c>
-      <c r="G133">
+      <c r="G133" s="1">
         <v>-10</v>
       </c>
-      <c r="H133">
+      <c r="H133" s="1">
         <v>31</v>
       </c>
-      <c r="I133">
+      <c r="I133" s="1">
         <v>5</v>
       </c>
-      <c r="J133" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="J133" s="3">
+        <v>0</v>
+      </c>
+      <c r="K133" s="1"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C134" s="1">
+      <c r="B134" s="1"/>
+      <c r="C134" s="2">
         <v>46261</v>
       </c>
-      <c r="D134" s="1">
+      <c r="D134" s="2">
         <v>46289</v>
       </c>
-      <c r="E134" s="1">
+      <c r="E134" s="2">
         <v>46238</v>
       </c>
-      <c r="F134" s="1">
+      <c r="F134" s="2">
         <v>46266</v>
       </c>
-      <c r="G134">
-        <v>-17</v>
-      </c>
-      <c r="H134">
-        <v>-17</v>
-      </c>
-      <c r="I134">
+      <c r="G134" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H134" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I134" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="J134" s="1"/>
+      <c r="K134" s="1"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C135" s="1">
+      <c r="C135" s="2">
         <v>46261</v>
       </c>
-      <c r="E135" s="1">
+      <c r="D135" s="1"/>
+      <c r="E135" s="2">
         <v>46238</v>
       </c>
-      <c r="G135">
-        <v>-17</v>
-      </c>
-      <c r="H135">
-        <v>-17</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="F135" s="1"/>
+      <c r="G135" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H135" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I135" s="1">
+        <v>0</v>
+      </c>
+      <c r="J135" s="3">
+        <v>0</v>
+      </c>
+      <c r="K135" s="1"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C136" s="1">
+      <c r="C136" s="2">
         <v>46261</v>
       </c>
-      <c r="D136" s="1">
+      <c r="D136" s="2">
         <v>46275</v>
       </c>
-      <c r="E136" s="1">
+      <c r="E136" s="2">
         <v>46238</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F136" s="2">
         <v>46251</v>
       </c>
-      <c r="G136">
-        <v>-17</v>
-      </c>
-      <c r="H136">
-        <v>-17</v>
-      </c>
-      <c r="I136">
+      <c r="G136" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H136" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I136" s="1">
         <v>10</v>
       </c>
-      <c r="J136" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="J136" s="3">
+        <v>0</v>
+      </c>
+      <c r="K136" s="1"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C137" s="1">
+      <c r="C137" s="2">
         <v>46276</v>
       </c>
-      <c r="D137" s="1">
+      <c r="D137" s="2">
         <v>46289</v>
       </c>
-      <c r="E137" s="1">
+      <c r="E137" s="2">
         <v>46252</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F137" s="2">
         <v>46266</v>
       </c>
-      <c r="G137">
-        <v>-17</v>
-      </c>
-      <c r="H137">
-        <v>-17</v>
-      </c>
-      <c r="I137">
+      <c r="G137" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H137" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I137" s="1">
         <v>10</v>
       </c>
-      <c r="J137" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="J137" s="3">
+        <v>0</v>
+      </c>
+      <c r="K137" s="1"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D138" s="1">
+      <c r="C138" s="1"/>
+      <c r="D138" s="2">
         <v>46289</v>
       </c>
-      <c r="F138" s="1">
+      <c r="E138" s="1"/>
+      <c r="F138" s="2">
         <v>46266</v>
       </c>
-      <c r="G138">
-        <v>-17</v>
-      </c>
-      <c r="H138">
-        <v>-17</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="G138" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H138" s="1">
+        <v>-17</v>
+      </c>
+      <c r="I138" s="1">
+        <v>0</v>
+      </c>
+      <c r="J138" s="3">
+        <v>0</v>
+      </c>
+      <c r="K138" s="1"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C139" t="s">
+      <c r="B139" s="1"/>
+      <c r="C139" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D139" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E139" s="1">
+      <c r="E139" s="2">
         <v>46094</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F139" s="2">
         <v>46101</v>
       </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="G139" s="1">
+        <v>0</v>
+      </c>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1">
+        <v>0</v>
+      </c>
+      <c r="J139" s="1"/>
+      <c r="K139" s="1"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E140" s="1">
+      <c r="D140" s="1"/>
+      <c r="E140" s="2">
         <v>46094</v>
       </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140" s="2">
+      <c r="F140" s="1"/>
+      <c r="G140" s="1">
+        <v>0</v>
+      </c>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1">
+        <v>0</v>
+      </c>
+      <c r="J140" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="K140" s="1"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E141" s="1">
+      <c r="D141" s="1"/>
+      <c r="E141" s="2">
         <v>46101</v>
       </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141" s="2">
+      <c r="F141" s="1"/>
+      <c r="G141" s="1">
+        <v>0</v>
+      </c>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1">
+        <v>0</v>
+      </c>
+      <c r="J141" s="3">
         <v>1</v>
       </c>
+      <c r="K141" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/CL32.xlsx
+++ b/data/CL32.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adane\dm_tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1659496F-8D71-45C7-9514-9CD9329E8466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0268A98-EE7E-4358-98FB-F198E79A42FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="116">
   <si>
     <t>Activity Name</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>16-Mar-26 A</t>
-  </si>
-  <si>
-    <t>29-Apr-26 A</t>
   </si>
   <si>
     <t>13-May-26 A</t>
@@ -845,13 +842,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -866,10 +863,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46111</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -893,10 +890,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
@@ -920,7 +917,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>9</v>
@@ -947,13 +944,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="D6" s="2">
         <v>46136</v>
@@ -974,10 +971,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C7" s="2">
         <v>46178</v>
@@ -1003,10 +1000,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2">
         <v>46178</v>
@@ -1032,10 +1029,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="2">
@@ -1055,7 +1052,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2">
         <v>46174</v>
@@ -1084,13 +1081,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="2">
         <v>46111</v>
@@ -1111,13 +1108,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2">
         <v>46111</v>
@@ -1138,13 +1135,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2">
         <v>46111</v>
@@ -1165,13 +1162,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14" s="2">
         <v>46111</v>
@@ -1192,7 +1189,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
@@ -1217,7 +1214,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2">
         <v>46174</v>
@@ -1246,7 +1243,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2">
         <v>46181</v>
@@ -1275,7 +1272,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2">
         <v>46188</v>
@@ -1304,7 +1301,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="2">
         <v>46202</v>
@@ -1333,10 +1330,10 @@
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C20" s="2">
         <v>46213</v>
@@ -1360,13 +1357,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="2">
         <v>46111</v>
@@ -1387,13 +1384,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="D22" s="2">
         <v>46119</v>
@@ -1414,13 +1411,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="D23" s="2">
         <v>46126</v>
@@ -1441,13 +1438,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="D24" s="2">
         <v>46133</v>
@@ -1468,10 +1465,10 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C25" s="2">
         <v>46174</v>
@@ -1497,7 +1494,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="2">
         <v>46188</v>
@@ -1526,10 +1523,10 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>9</v>
@@ -1553,13 +1550,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D28" s="2">
         <v>46125</v>
@@ -1580,13 +1577,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C29" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D29" s="2">
         <v>46139</v>
@@ -1607,10 +1604,10 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -1626,11 +1623,11 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -1645,13 +1642,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="D32" s="2">
         <v>46104</v>
@@ -1672,13 +1669,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D33" s="2">
         <v>46111</v>
@@ -1699,13 +1696,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D34" s="2">
         <v>46132</v>
@@ -1726,7 +1723,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B35" s="2">
         <v>46202</v>
@@ -1751,7 +1748,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B36" s="2">
         <v>46202</v>
@@ -1780,7 +1777,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>13</v>
@@ -1807,7 +1804,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>13</v>
@@ -1834,7 +1831,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>13</v>
@@ -1861,7 +1858,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B40" s="2">
         <v>46188</v>
@@ -1890,7 +1887,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B41" s="2">
         <v>46195</v>
@@ -1919,7 +1916,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2">
         <v>46216</v>
@@ -1946,7 +1943,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B43" s="2">
         <v>46216</v>
@@ -1973,7 +1970,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B44" s="2">
         <v>46216</v>
@@ -2002,7 +1999,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B45" s="2">
         <v>46230</v>
@@ -2031,7 +2028,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B46" s="2">
         <v>46237</v>
@@ -2060,7 +2057,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B47" s="2">
         <v>46251</v>
@@ -2089,7 +2086,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B48" s="2">
         <v>46216</v>
@@ -2118,7 +2115,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B49" s="2">
         <v>46225</v>
@@ -2147,7 +2144,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B50" s="2">
         <v>46232</v>
@@ -2176,7 +2173,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B51" s="2">
         <v>46239</v>
@@ -2205,7 +2202,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B52" s="2">
         <v>46246</v>
@@ -2234,7 +2231,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B53" s="2">
         <v>46253</v>
@@ -2263,7 +2260,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B54" s="2">
         <v>46216</v>
@@ -2292,7 +2289,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B55" s="2">
         <v>46258</v>
@@ -2321,7 +2318,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B56" s="2">
         <v>46237</v>
@@ -2350,7 +2347,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B57" s="2">
         <v>46174</v>
@@ -2379,7 +2376,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B58" s="2">
         <v>46174</v>
@@ -2408,7 +2405,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B59" s="2">
         <v>46216</v>
@@ -2437,7 +2434,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B60" s="2">
         <v>46237</v>
@@ -2466,7 +2463,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B61" s="2">
         <v>46237</v>
@@ -2495,7 +2492,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B62" s="2">
         <v>46216</v>
@@ -2524,7 +2521,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B63" s="2">
         <v>46219</v>
@@ -2553,7 +2550,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B64" s="2">
         <v>46224</v>
@@ -2582,7 +2579,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B65" s="2">
         <v>46227</v>
@@ -2611,7 +2608,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B66" s="2">
         <v>46232</v>
@@ -2640,7 +2637,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B67" s="2">
         <v>46232</v>
@@ -2669,10 +2666,10 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -2688,13 +2685,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C69" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D69" s="2">
         <v>46139</v>
@@ -2715,13 +2712,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D70" s="2">
         <v>46154</v>
@@ -2742,10 +2739,10 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C71" s="2">
         <v>46175</v>
@@ -2771,10 +2768,10 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C72" s="2">
         <v>46184</v>
@@ -2800,7 +2797,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B73" s="2">
         <v>46176</v>
@@ -2829,7 +2826,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B74" s="2">
         <v>46185</v>
@@ -2858,7 +2855,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B75" s="2">
         <v>46199</v>
@@ -2887,10 +2884,10 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C76" s="2">
         <v>46177</v>
@@ -2916,7 +2913,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B77" s="2">
         <v>46181</v>
@@ -2945,7 +2942,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B78" s="2">
         <v>46188</v>
@@ -2974,7 +2971,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B79" s="2">
         <v>46261</v>
@@ -2999,7 +2996,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B80" s="2">
         <v>46261</v>
@@ -3028,7 +3025,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B81" s="2">
         <v>46276</v>
@@ -3057,7 +3054,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="2">

--- a/data/CL32.xlsx
+++ b/data/CL32.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adane\dm_tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0575C4BC-681B-4C10-B39B-5486C868F104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E11B47A-C905-4C0E-B4B4-326B45358D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
+    <workbookView xWindow="0" yWindow="390" windowWidth="12570" windowHeight="14745" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="290">
   <si>
     <t>Activity ID</t>
   </si>
@@ -71,9 +71,6 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>Ferry PS Updated Scope May 26 CL32 Programme</t>
-  </si>
-  <si>
     <t>16-Feb-26 A</t>
   </si>
   <si>
@@ -906,6 +903,9 @@
   </si>
   <si>
     <t>07-Oct-26*</t>
+  </si>
+  <si>
+    <t>FPS Updated Scope May 26 CL32 Programme</t>
   </si>
 </sst>
 </file>
@@ -1285,7 +1285,8 @@
   <cols>
     <col min="1" max="1" width="46.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="96.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -1331,10 +1332,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
+        <v>289</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46069</v>
       </c>
       <c r="D2" s="1">
         <v>46302</v>
@@ -1357,10 +1358,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1">
         <v>46302</v>
@@ -1383,10 +1384,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1">
         <v>46302</v>
@@ -1409,13 +1410,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1">
         <v>46069</v>
@@ -1432,10 +1433,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
       </c>
       <c r="C6" s="1">
         <v>46290</v>
@@ -1464,14 +1465,14 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1">
@@ -1492,7 +1493,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1">
         <v>46185</v>
@@ -1518,10 +1519,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
       </c>
       <c r="D9" s="1">
         <v>46185</v>
@@ -1544,10 +1545,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
         <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
       </c>
       <c r="D10" s="1">
         <v>46202</v>
@@ -1570,10 +1571,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
         <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
       </c>
       <c r="D11" s="1">
         <v>46289</v>
@@ -1596,10 +1597,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
       </c>
       <c r="D12" s="1">
         <v>46289</v>
@@ -1622,13 +1623,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
         <v>30</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>31</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
       </c>
       <c r="E13" s="1">
         <v>46122</v>
@@ -1645,13 +1646,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
         <v>33</v>
       </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1">
         <v>46122</v>
@@ -1668,18 +1669,15 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
         <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D16" s="1">
         <v>46135</v>
@@ -1696,13 +1694,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
         <v>39</v>
       </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1713,10 +1711,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1">
         <v>46174</v>
@@ -1739,13 +1737,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
         <v>42</v>
       </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1">
         <v>46069</v>
@@ -1762,13 +1760,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
         <v>44</v>
       </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1">
         <v>46069</v>
@@ -1785,13 +1783,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
         <v>46</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>47</v>
-      </c>
-      <c r="C21" t="s">
-        <v>48</v>
       </c>
       <c r="E21" s="1">
         <v>46093</v>
@@ -1808,13 +1806,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
         <v>49</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>50</v>
-      </c>
-      <c r="C22" t="s">
-        <v>51</v>
       </c>
       <c r="E22" s="1">
         <v>46094</v>
@@ -1831,13 +1829,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
         <v>52</v>
       </c>
-      <c r="B23" t="s">
-        <v>53</v>
-      </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E23" s="1">
         <v>46094</v>
@@ -1854,13 +1852,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
         <v>54</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>55</v>
-      </c>
-      <c r="C24" t="s">
-        <v>56</v>
       </c>
       <c r="E24" s="1">
         <v>46101</v>
@@ -1877,13 +1875,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" t="s">
         <v>57</v>
       </c>
-      <c r="B25" t="s">
-        <v>58</v>
-      </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E25" s="1">
         <v>46101</v>
@@ -1900,13 +1898,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
         <v>59</v>
       </c>
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E26" s="1">
         <v>46101</v>
@@ -1923,13 +1921,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
         <v>61</v>
       </c>
-      <c r="B27" t="s">
-        <v>62</v>
-      </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27" s="1">
         <v>46101</v>
@@ -1946,13 +1944,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" t="s">
         <v>63</v>
       </c>
-      <c r="B28" t="s">
-        <v>64</v>
-      </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E28" s="1">
         <v>46101</v>
@@ -1969,13 +1967,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
         <v>65</v>
       </c>
-      <c r="B29" t="s">
-        <v>66</v>
-      </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E29" s="1">
         <v>46101</v>
@@ -1992,13 +1990,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
         <v>67</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>68</v>
-      </c>
-      <c r="C30" t="s">
-        <v>69</v>
       </c>
       <c r="E30" s="1">
         <v>46143</v>
@@ -2018,13 +2016,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
         <v>70</v>
-      </c>
-      <c r="C31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" t="s">
-        <v>71</v>
       </c>
       <c r="E31" s="1">
         <v>46069</v>
@@ -2041,16 +2039,16 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" t="s">
         <v>72</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
         <v>73</v>
-      </c>
-      <c r="C32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" t="s">
-        <v>74</v>
       </c>
       <c r="E32" s="1">
         <v>46069</v>
@@ -2070,16 +2068,16 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" t="s">
         <v>75</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>76</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>77</v>
-      </c>
-      <c r="D33" t="s">
-        <v>78</v>
       </c>
       <c r="E33" s="1">
         <v>46076</v>
@@ -2099,16 +2097,16 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
         <v>79</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>80</v>
       </c>
-      <c r="C34" t="s">
-        <v>81</v>
-      </c>
       <c r="D34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E34" s="1">
         <v>46090</v>
@@ -2128,16 +2126,16 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" t="s">
         <v>82</v>
       </c>
-      <c r="B35" t="s">
-        <v>83</v>
-      </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E35" s="1">
         <v>46090</v>
@@ -2157,16 +2155,16 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" t="s">
         <v>84</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>85</v>
       </c>
-      <c r="C36" t="s">
-        <v>86</v>
-      </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E36" s="1">
         <v>46097</v>
@@ -2186,10 +2184,10 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D37" s="1">
         <v>46289</v>
@@ -2212,13 +2210,13 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" t="s">
         <v>88</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>89</v>
-      </c>
-      <c r="D38" t="s">
-        <v>90</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2226,16 +2224,16 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" t="s">
         <v>91</v>
       </c>
-      <c r="B39" t="s">
-        <v>92</v>
-      </c>
       <c r="C39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39" t="s">
         <v>89</v>
-      </c>
-      <c r="D39" t="s">
-        <v>90</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2246,10 +2244,10 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" t="s">
         <v>93</v>
-      </c>
-      <c r="C40" t="s">
-        <v>94</v>
       </c>
       <c r="D40" s="1">
         <v>46185</v>
@@ -2272,16 +2270,16 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" t="s">
         <v>95</v>
       </c>
-      <c r="B41" t="s">
-        <v>96</v>
-      </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E41" s="1">
         <v>46111</v>
@@ -2301,16 +2299,16 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" t="s">
         <v>97</v>
       </c>
-      <c r="B42" t="s">
-        <v>98</v>
-      </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E42" s="1">
         <v>46111</v>
@@ -2330,16 +2328,16 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" t="s">
         <v>99</v>
       </c>
-      <c r="B43" t="s">
-        <v>100</v>
-      </c>
       <c r="C43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E43" s="1">
         <v>46122</v>
@@ -2359,16 +2357,16 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" t="s">
         <v>101</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>102</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>103</v>
-      </c>
-      <c r="D44" t="s">
-        <v>104</v>
       </c>
       <c r="E44" s="1">
         <v>46136</v>
@@ -2388,13 +2386,13 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" t="s">
         <v>105</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>106</v>
-      </c>
-      <c r="C45" t="s">
-        <v>107</v>
       </c>
       <c r="D45" s="1">
         <v>46178</v>
@@ -2420,13 +2418,13 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" t="s">
         <v>108</v>
       </c>
-      <c r="B46" t="s">
-        <v>109</v>
-      </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D46" s="1">
         <v>46178</v>
@@ -2452,13 +2450,13 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>109</v>
+      </c>
+      <c r="B47" t="s">
         <v>110</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>111</v>
-      </c>
-      <c r="C47" t="s">
-        <v>112</v>
       </c>
       <c r="E47" s="1">
         <v>46143</v>
@@ -2473,15 +2471,15 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" t="s">
         <v>114</v>
-      </c>
-      <c r="B48" t="s">
-        <v>115</v>
       </c>
       <c r="C48" s="1">
         <v>46174</v>
@@ -2510,10 +2508,10 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D49" s="1">
         <v>46206</v>
@@ -2536,16 +2534,16 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" t="s">
         <v>117</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
+        <v>93</v>
+      </c>
+      <c r="D50" t="s">
         <v>118</v>
-      </c>
-      <c r="C50" t="s">
-        <v>94</v>
-      </c>
-      <c r="D50" t="s">
-        <v>119</v>
       </c>
       <c r="E50" s="1">
         <v>46111</v>
@@ -2565,16 +2563,16 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" t="s">
         <v>120</v>
       </c>
-      <c r="B51" t="s">
-        <v>121</v>
-      </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E51" s="1">
         <v>46111</v>
@@ -2594,16 +2592,16 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>121</v>
+      </c>
+      <c r="B52" t="s">
         <v>122</v>
       </c>
-      <c r="B52" t="s">
-        <v>123</v>
-      </c>
       <c r="C52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D52" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E52" s="1">
         <v>46111</v>
@@ -2623,16 +2621,16 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" t="s">
         <v>124</v>
       </c>
-      <c r="B53" t="s">
-        <v>125</v>
-      </c>
       <c r="C53" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D53" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E53" s="1">
         <v>46111</v>
@@ -2652,13 +2650,13 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" t="s">
         <v>126</v>
       </c>
-      <c r="B54" t="s">
-        <v>127</v>
-      </c>
       <c r="D54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F54" s="1">
         <v>46147</v>
@@ -2676,15 +2674,15 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" t="s">
         <v>129</v>
-      </c>
-      <c r="B55" t="s">
-        <v>130</v>
       </c>
       <c r="C55" s="1">
         <v>46174</v>
@@ -2713,10 +2711,10 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>130</v>
+      </c>
+      <c r="B56" t="s">
         <v>131</v>
-      </c>
-      <c r="B56" t="s">
-        <v>132</v>
       </c>
       <c r="C56" s="1">
         <v>46181</v>
@@ -2745,10 +2743,10 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>132</v>
+      </c>
+      <c r="B57" t="s">
         <v>133</v>
-      </c>
-      <c r="B57" t="s">
-        <v>134</v>
       </c>
       <c r="C57" s="1">
         <v>46188</v>
@@ -2777,10 +2775,10 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" t="s">
         <v>135</v>
-      </c>
-      <c r="B58" t="s">
-        <v>136</v>
       </c>
       <c r="C58" s="1">
         <v>46202</v>
@@ -2809,10 +2807,10 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" t="s">
         <v>137</v>
-      </c>
-      <c r="C59" t="s">
-        <v>138</v>
       </c>
       <c r="D59" s="1">
         <v>46213</v>
@@ -2835,10 +2833,10 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D60" s="1">
         <v>46199</v>
@@ -2861,16 +2859,16 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>139</v>
+      </c>
+      <c r="B61" t="s">
         <v>140</v>
       </c>
-      <c r="B61" t="s">
-        <v>141</v>
-      </c>
       <c r="C61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D61" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E61" s="1">
         <v>46111</v>
@@ -2890,16 +2888,16 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B62" t="s">
         <v>142</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>143</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>144</v>
-      </c>
-      <c r="D62" t="s">
-        <v>145</v>
       </c>
       <c r="E62" s="1">
         <v>46119</v>
@@ -2919,16 +2917,16 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>145</v>
+      </c>
+      <c r="B63" t="s">
         <v>146</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>147</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>148</v>
-      </c>
-      <c r="D63" t="s">
-        <v>149</v>
       </c>
       <c r="E63" s="1">
         <v>46126</v>
@@ -2948,16 +2946,16 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>149</v>
+      </c>
+      <c r="B64" t="s">
         <v>150</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>151</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>152</v>
-      </c>
-      <c r="D64" t="s">
-        <v>153</v>
       </c>
       <c r="E64" s="1">
         <v>46133</v>
@@ -2977,13 +2975,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>153</v>
+      </c>
+      <c r="B65" t="s">
         <v>154</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>155</v>
-      </c>
-      <c r="C65" t="s">
-        <v>156</v>
       </c>
       <c r="D65" s="1">
         <v>46174</v>
@@ -3009,10 +3007,10 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>156</v>
+      </c>
+      <c r="B66" t="s">
         <v>157</v>
-      </c>
-      <c r="B66" t="s">
-        <v>158</v>
       </c>
       <c r="C66" s="1">
         <v>46188</v>
@@ -3041,13 +3039,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D67" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E67" s="1">
         <v>46111</v>
@@ -3064,16 +3062,16 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>159</v>
+      </c>
+      <c r="B68" t="s">
         <v>160</v>
       </c>
-      <c r="B68" t="s">
-        <v>161</v>
-      </c>
       <c r="C68" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E68" s="1">
         <v>46111</v>
@@ -3093,16 +3091,16 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>161</v>
+      </c>
+      <c r="B69" t="s">
         <v>162</v>
       </c>
-      <c r="B69" t="s">
-        <v>163</v>
-      </c>
       <c r="C69" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E69" s="1">
         <v>46125</v>
@@ -3122,16 +3120,16 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>163</v>
+      </c>
+      <c r="B70" t="s">
         <v>164</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>165</v>
       </c>
-      <c r="C70" t="s">
-        <v>166</v>
-      </c>
       <c r="D70" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E70" s="1">
         <v>46139</v>
@@ -3151,13 +3149,13 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>166</v>
+      </c>
+      <c r="B71" t="s">
         <v>167</v>
       </c>
-      <c r="B71" t="s">
-        <v>168</v>
-      </c>
       <c r="C71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3168,13 +3166,13 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>168</v>
+      </c>
+      <c r="B72" t="s">
         <v>169</v>
       </c>
-      <c r="B72" t="s">
+      <c r="D72" t="s">
         <v>170</v>
-      </c>
-      <c r="D72" t="s">
-        <v>171</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3185,13 +3183,13 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C73" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D73" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E73" s="1">
         <v>46104</v>
@@ -3208,16 +3206,16 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>172</v>
+      </c>
+      <c r="B74" t="s">
         <v>173</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
+        <v>137</v>
+      </c>
+      <c r="D74" t="s">
         <v>174</v>
-      </c>
-      <c r="C74" t="s">
-        <v>138</v>
-      </c>
-      <c r="D74" t="s">
-        <v>175</v>
       </c>
       <c r="E74" s="1">
         <v>46104</v>
@@ -3237,16 +3235,16 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>175</v>
+      </c>
+      <c r="B75" t="s">
         <v>176</v>
       </c>
-      <c r="B75" t="s">
-        <v>177</v>
-      </c>
       <c r="C75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E75" s="1">
         <v>46111</v>
@@ -3266,16 +3264,16 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>177</v>
+      </c>
+      <c r="B76" t="s">
         <v>178</v>
       </c>
-      <c r="B76" t="s">
-        <v>179</v>
-      </c>
       <c r="C76" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D76" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E76" s="1">
         <v>46132</v>
@@ -3295,7 +3293,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C77" s="1">
         <v>46202</v>
@@ -3321,10 +3319,10 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>180</v>
+      </c>
+      <c r="B78" t="s">
         <v>181</v>
-      </c>
-      <c r="B78" t="s">
-        <v>182</v>
       </c>
       <c r="C78" s="1">
         <v>46202</v>
@@ -3347,10 +3345,10 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>182</v>
+      </c>
+      <c r="B79" t="s">
         <v>183</v>
-      </c>
-      <c r="B79" t="s">
-        <v>184</v>
       </c>
       <c r="C79" s="1">
         <v>46202</v>
@@ -3379,10 +3377,10 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D80" s="1">
         <v>46289</v>
@@ -3405,10 +3403,10 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D81" s="1">
         <v>46206</v>
@@ -3431,16 +3429,16 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>186</v>
+      </c>
+      <c r="B82" t="s">
         <v>187</v>
       </c>
-      <c r="B82" t="s">
-        <v>188</v>
-      </c>
       <c r="C82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D82" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E82" s="1">
         <v>46097</v>
@@ -3460,10 +3458,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>188</v>
+      </c>
+      <c r="B83" t="s">
         <v>189</v>
-      </c>
-      <c r="B83" t="s">
-        <v>190</v>
       </c>
       <c r="C83" s="1">
         <v>46188</v>
@@ -3492,10 +3490,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>190</v>
+      </c>
+      <c r="B84" t="s">
         <v>191</v>
-      </c>
-      <c r="B84" t="s">
-        <v>192</v>
       </c>
       <c r="C84" s="1">
         <v>46195</v>
@@ -3524,7 +3522,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C85" s="1">
         <v>46216</v>
@@ -3550,7 +3548,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C86" s="1">
         <v>46216</v>
@@ -3576,10 +3574,10 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>193</v>
+      </c>
+      <c r="B87" t="s">
         <v>194</v>
-      </c>
-      <c r="B87" t="s">
-        <v>195</v>
       </c>
       <c r="C87" s="1">
         <v>46216</v>
@@ -3608,10 +3606,10 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>195</v>
+      </c>
+      <c r="B88" t="s">
         <v>196</v>
-      </c>
-      <c r="B88" t="s">
-        <v>197</v>
       </c>
       <c r="C88" s="1">
         <v>46230</v>
@@ -3640,10 +3638,10 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>197</v>
+      </c>
+      <c r="B89" t="s">
         <v>198</v>
-      </c>
-      <c r="B89" t="s">
-        <v>199</v>
       </c>
       <c r="C89" s="1">
         <v>46237</v>
@@ -3672,10 +3670,10 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>199</v>
+      </c>
+      <c r="B90" t="s">
         <v>200</v>
-      </c>
-      <c r="B90" t="s">
-        <v>201</v>
       </c>
       <c r="C90" s="1">
         <v>46251</v>
@@ -3704,7 +3702,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C91" s="1">
         <v>46216</v>
@@ -3730,10 +3728,10 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>202</v>
+      </c>
+      <c r="B92" t="s">
         <v>203</v>
-      </c>
-      <c r="B92" t="s">
-        <v>204</v>
       </c>
       <c r="C92" s="1">
         <v>46216</v>
@@ -3762,10 +3760,10 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>204</v>
+      </c>
+      <c r="B93" t="s">
         <v>205</v>
-      </c>
-      <c r="B93" t="s">
-        <v>206</v>
       </c>
       <c r="C93" s="1">
         <v>46225</v>
@@ -3794,10 +3792,10 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>206</v>
+      </c>
+      <c r="B94" t="s">
         <v>207</v>
-      </c>
-      <c r="B94" t="s">
-        <v>208</v>
       </c>
       <c r="C94" s="1">
         <v>46232</v>
@@ -3826,7 +3824,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C95" s="1">
         <v>46239</v>
@@ -3852,10 +3850,10 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>209</v>
+      </c>
+      <c r="B96" t="s">
         <v>210</v>
-      </c>
-      <c r="B96" t="s">
-        <v>211</v>
       </c>
       <c r="C96" s="1">
         <v>46239</v>
@@ -3884,10 +3882,10 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>211</v>
+      </c>
+      <c r="B97" t="s">
         <v>212</v>
-      </c>
-      <c r="B97" t="s">
-        <v>213</v>
       </c>
       <c r="C97" s="1">
         <v>46246</v>
@@ -3916,10 +3914,10 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>213</v>
+      </c>
+      <c r="B98" t="s">
         <v>214</v>
-      </c>
-      <c r="B98" t="s">
-        <v>215</v>
       </c>
       <c r="C98" s="1">
         <v>46253</v>
@@ -3948,7 +3946,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C99" s="1">
         <v>46216</v>
@@ -3974,10 +3972,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>216</v>
+      </c>
+      <c r="B100" t="s">
         <v>217</v>
-      </c>
-      <c r="B100" t="s">
-        <v>218</v>
       </c>
       <c r="C100" s="1">
         <v>46216</v>
@@ -4006,7 +4004,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C101" s="1">
         <v>46258</v>
@@ -4032,10 +4030,10 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>219</v>
+      </c>
+      <c r="B102" t="s">
         <v>220</v>
-      </c>
-      <c r="B102" t="s">
-        <v>221</v>
       </c>
       <c r="C102" s="1">
         <v>46258</v>
@@ -4064,7 +4062,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C103" s="1">
         <v>46237</v>
@@ -4090,10 +4088,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>222</v>
+      </c>
+      <c r="B104" t="s">
         <v>223</v>
-      </c>
-      <c r="B104" t="s">
-        <v>224</v>
       </c>
       <c r="C104" s="1">
         <v>46237</v>
@@ -4122,7 +4120,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C105" s="1">
         <v>46174</v>
@@ -4148,10 +4146,10 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>225</v>
+      </c>
+      <c r="B106" t="s">
         <v>226</v>
-      </c>
-      <c r="B106" t="s">
-        <v>227</v>
       </c>
       <c r="C106" s="1">
         <v>46174</v>
@@ -4180,10 +4178,10 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>227</v>
+      </c>
+      <c r="B107" t="s">
         <v>228</v>
-      </c>
-      <c r="B107" t="s">
-        <v>229</v>
       </c>
       <c r="C107" s="1">
         <v>46174</v>
@@ -4212,7 +4210,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C108" s="1">
         <v>46216</v>
@@ -4238,7 +4236,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C109" s="1">
         <v>46216</v>
@@ -4264,10 +4262,10 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>231</v>
+      </c>
+      <c r="B110" t="s">
         <v>232</v>
-      </c>
-      <c r="B110" t="s">
-        <v>233</v>
       </c>
       <c r="C110" s="1">
         <v>46216</v>
@@ -4296,10 +4294,10 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>233</v>
+      </c>
+      <c r="B111" t="s">
         <v>234</v>
-      </c>
-      <c r="B111" t="s">
-        <v>235</v>
       </c>
       <c r="C111" s="1">
         <v>46237</v>
@@ -4328,10 +4326,10 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>235</v>
+      </c>
+      <c r="B112" t="s">
         <v>236</v>
-      </c>
-      <c r="B112" t="s">
-        <v>237</v>
       </c>
       <c r="C112" s="1">
         <v>46237</v>
@@ -4360,7 +4358,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C113" s="1">
         <v>46216</v>
@@ -4386,10 +4384,10 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>238</v>
+      </c>
+      <c r="B114" t="s">
         <v>239</v>
-      </c>
-      <c r="B114" t="s">
-        <v>240</v>
       </c>
       <c r="C114" s="1">
         <v>46216</v>
@@ -4418,10 +4416,10 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>240</v>
+      </c>
+      <c r="B115" t="s">
         <v>241</v>
-      </c>
-      <c r="B115" t="s">
-        <v>242</v>
       </c>
       <c r="C115" s="1">
         <v>46219</v>
@@ -4450,10 +4448,10 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>242</v>
+      </c>
+      <c r="B116" t="s">
         <v>243</v>
-      </c>
-      <c r="B116" t="s">
-        <v>244</v>
       </c>
       <c r="C116" s="1">
         <v>46224</v>
@@ -4482,10 +4480,10 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>244</v>
+      </c>
+      <c r="B117" t="s">
         <v>245</v>
-      </c>
-      <c r="B117" t="s">
-        <v>246</v>
       </c>
       <c r="C117" s="1">
         <v>46227</v>
@@ -4514,10 +4512,10 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>246</v>
+      </c>
+      <c r="B118" t="s">
         <v>247</v>
-      </c>
-      <c r="B118" t="s">
-        <v>248</v>
       </c>
       <c r="C118" s="1">
         <v>46232</v>
@@ -4546,10 +4544,10 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>248</v>
+      </c>
+      <c r="B119" t="s">
         <v>249</v>
-      </c>
-      <c r="B119" t="s">
-        <v>250</v>
       </c>
       <c r="C119" s="1">
         <v>46232</v>
@@ -4578,10 +4576,10 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>250</v>
+      </c>
+      <c r="C120" t="s">
         <v>251</v>
-      </c>
-      <c r="C120" t="s">
-        <v>252</v>
       </c>
       <c r="D120" s="1">
         <v>46205</v>
@@ -4604,10 +4602,10 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C121" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D121" s="1">
         <v>46205</v>
@@ -4630,13 +4628,13 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>252</v>
+      </c>
+      <c r="B122" t="s">
         <v>253</v>
       </c>
-      <c r="B122" t="s">
-        <v>254</v>
-      </c>
       <c r="C122" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I122">
         <v>0</v>
@@ -4647,16 +4645,16 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>254</v>
+      </c>
+      <c r="B123" t="s">
         <v>255</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>256</v>
       </c>
-      <c r="C123" t="s">
-        <v>257</v>
-      </c>
       <c r="D123" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E123" s="1">
         <v>46139</v>
@@ -4676,16 +4674,16 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>257</v>
+      </c>
+      <c r="B124" t="s">
         <v>258</v>
       </c>
-      <c r="B124" t="s">
-        <v>259</v>
-      </c>
       <c r="C124" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D124" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E124" s="1">
         <v>46154</v>
@@ -4705,13 +4703,13 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>259</v>
+      </c>
+      <c r="B125" t="s">
         <v>260</v>
       </c>
-      <c r="B125" t="s">
-        <v>261</v>
-      </c>
       <c r="C125" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D125" s="1">
         <v>46175</v>
@@ -4737,13 +4735,13 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>261</v>
+      </c>
+      <c r="B126" t="s">
         <v>262</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>263</v>
-      </c>
-      <c r="C126" t="s">
-        <v>264</v>
       </c>
       <c r="D126" s="1">
         <v>46184</v>
@@ -4769,10 +4767,10 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>264</v>
+      </c>
+      <c r="B127" t="s">
         <v>265</v>
-      </c>
-      <c r="B127" t="s">
-        <v>266</v>
       </c>
       <c r="C127" s="1">
         <v>46176</v>
@@ -4801,10 +4799,10 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>266</v>
+      </c>
+      <c r="B128" t="s">
         <v>267</v>
-      </c>
-      <c r="B128" t="s">
-        <v>268</v>
       </c>
       <c r="C128" s="1">
         <v>46185</v>
@@ -4833,10 +4831,10 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>268</v>
+      </c>
+      <c r="B129" t="s">
         <v>269</v>
-      </c>
-      <c r="B129" t="s">
-        <v>270</v>
       </c>
       <c r="C129" s="1">
         <v>46199</v>
@@ -4865,10 +4863,10 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C130" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D130" s="1">
         <v>46192</v>
@@ -4891,13 +4889,13 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>270</v>
+      </c>
+      <c r="B131" t="s">
         <v>271</v>
       </c>
-      <c r="B131" t="s">
-        <v>272</v>
-      </c>
       <c r="C131" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D131" s="1">
         <v>46177</v>
@@ -4923,10 +4921,10 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>272</v>
+      </c>
+      <c r="B132" t="s">
         <v>273</v>
-      </c>
-      <c r="B132" t="s">
-        <v>274</v>
       </c>
       <c r="C132" s="1">
         <v>46181</v>
@@ -4955,10 +4953,10 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>274</v>
+      </c>
+      <c r="B133" t="s">
         <v>275</v>
-      </c>
-      <c r="B133" t="s">
-        <v>276</v>
       </c>
       <c r="C133" s="1">
         <v>46188</v>
@@ -4987,7 +4985,7 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C134" s="1">
         <v>46261</v>
@@ -5013,10 +5011,10 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B135" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C135" s="1">
         <v>46261</v>
@@ -5039,10 +5037,10 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B136" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C136" s="1">
         <v>46261</v>
@@ -5071,10 +5069,10 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>279</v>
+      </c>
+      <c r="B137" t="s">
         <v>280</v>
-      </c>
-      <c r="B137" t="s">
-        <v>281</v>
       </c>
       <c r="C137" s="1">
         <v>46276</v>
@@ -5103,10 +5101,10 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>281</v>
+      </c>
+      <c r="B138" t="s">
         <v>282</v>
-      </c>
-      <c r="B138" t="s">
-        <v>283</v>
       </c>
       <c r="D138" s="1">
         <v>46289</v>
@@ -5129,13 +5127,13 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C139" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D139" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E139" s="1">
         <v>46094</v>
@@ -5152,13 +5150,13 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>284</v>
+      </c>
+      <c r="B140" t="s">
         <v>285</v>
       </c>
-      <c r="B140" t="s">
-        <v>286</v>
-      </c>
       <c r="C140" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E140" s="1">
         <v>46094</v>
@@ -5175,13 +5173,13 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>286</v>
+      </c>
+      <c r="B141" t="s">
         <v>287</v>
       </c>
-      <c r="B141" t="s">
-        <v>288</v>
-      </c>
       <c r="C141" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E141" s="1">
         <v>46101</v>
